--- a/meal example emulsion drink.xlsx
+++ b/meal example emulsion drink.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90FB9A8-13C5-49A9-A4A3-C66A3EF66B09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454ECF98-5FFD-4642-8290-CEADEA954C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meal" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -497,7 +502,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -513,7 +518,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="meal"/>
@@ -642,7 +647,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1054,7 +1059,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7">
         <v>1</v>
